--- a/FINANCE.xlsx
+++ b/FINANCE.xlsx
@@ -428,29 +428,29 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>2</v>
+      <c r="A2" t="str">
+        <v/>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-15</v>
+        <v/>
       </c>
       <c r="C2" t="str">
-        <v>asset</v>
+        <v/>
       </c>
       <c r="D2" t="str">
-        <v>Bank Account</v>
+        <v/>
       </c>
       <c r="E2" t="str">
-        <v>Opening Balance</v>
-      </c>
-      <c r="F2">
-        <v>719</v>
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Opening Balance</v>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/FINANCE.xlsx
+++ b/FINANCE.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -428,34 +428,116 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
+      <c r="A2">
+        <v>3</v>
+      </c>
+      <c r="B2" t="str">
+        <v>2024-06-01</v>
+      </c>
+      <c r="C2" t="str">
+        <v>expense</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Rent</v>
+      </c>
+      <c r="E2" t="str">
+        <v>MAB CHARGE</v>
+      </c>
+      <c r="F2">
+        <v>300</v>
+      </c>
+      <c r="G2" t="str">
+        <v>SCREF00124238235</v>
+      </c>
+      <c r="H2" t="str">
+        <v>CA 101 MAB CHARGE</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>4</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2024-06-01</v>
+      </c>
+      <c r="C3" t="str">
+        <v>expense</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Utilities</v>
+      </c>
+      <c r="E3" t="str">
+        <v>GST</v>
+      </c>
+      <c r="F3">
+        <v>54</v>
+      </c>
+      <c r="G3" t="str">
+        <v>SCREF00124238235</v>
+      </c>
+      <c r="H3" t="str">
+        <v>GST paid to bank</v>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4">
+        <v>5</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2024-06-15</v>
+      </c>
+      <c r="C4" t="str">
+        <v>income</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Sales Revenue</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Prince Kumar</v>
+      </c>
+      <c r="F4">
+        <v>4000</v>
+      </c>
+      <c r="G4" t="str">
+        <v>C416789339494</v>
+      </c>
+      <c r="H4" t="str" xml:space="preserve">
+        <v xml:space="preserve">UPI/CR/C416789339494/PRINCE
+KUM/OKHD/PR9525425261
+3@OKHDFCBANK/UPI/HDF54949F9C
+CB3F44FC812E10A3B3379797</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5">
+        <v>6</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2024-06-30</v>
+      </c>
+      <c r="C5" t="str">
+        <v>income</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Sales Revenue</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Proposal Development - Jamaica Stock Exchange</v>
+      </c>
+      <c r="F5">
+        <v>31500</v>
+      </c>
+      <c r="G5" t="str">
         <v/>
       </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-      <c r="H2" t="str">
-        <v/>
+      <c r="H5" t="str" xml:space="preserve">
+        <v xml:space="preserve">NEFT CR-ICIC0SF0002-TUTECK
+TECHNOLOGIES-36783912691DC</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -748,7 +830,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/FINANCE.xlsx
+++ b/FINANCE.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -464,7 +464,7 @@
         <v>expense</v>
       </c>
       <c r="D3" t="str">
-        <v>Utilities</v>
+        <v>Rent</v>
       </c>
       <c r="E3" t="str">
         <v>GST</v>
@@ -535,9 +535,144 @@
 TECHNOLOGIES-36783912691DC</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6">
+        <v>7</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2024-07-01</v>
+      </c>
+      <c r="C6" t="str">
+        <v>expense</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Rent</v>
+      </c>
+      <c r="E6" t="str">
+        <v>MAB CHARGE</v>
+      </c>
+      <c r="F6">
+        <v>300</v>
+      </c>
+      <c r="G6" t="str">
+        <v>SCREF00138682650</v>
+      </c>
+      <c r="H6" t="str">
+        <v>MAB CHARGE - CA 101 MAB CHARGE</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>8</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2024-07-01</v>
+      </c>
+      <c r="C7" t="str">
+        <v>expense</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Rent</v>
+      </c>
+      <c r="E7" t="str">
+        <v>GST</v>
+      </c>
+      <c r="F7">
+        <v>54</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v>GST paid to bank</v>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8">
+        <v>9</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2024-07-05</v>
+      </c>
+      <c r="C8" t="str">
+        <v>expense</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Tanveer's Camera Shop</v>
+      </c>
+      <c r="F8">
+        <v>16500</v>
+      </c>
+      <c r="G8" t="str">
+        <v>STBATCH000067076 89</v>
+      </c>
+      <c r="H8" t="str" xml:space="preserve">
+        <v xml:space="preserve">CHQ PAID-CTS INWARD  CLEARING
+ZONE 8-TANVIRS THE CAMERA
+SHOPPE-HDFC BANK LTD.-HDFC
+BANK LTD</v>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9">
+        <v>10</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="C9" t="str">
+        <v>expense</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Salaries &amp; Wages</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Cash Withdrawal</v>
+      </c>
+      <c r="F9">
+        <v>3000</v>
+      </c>
+      <c r="G9" t="str">
+        <v>94314202407150077 00000045</v>
+      </c>
+      <c r="H9" t="str" xml:space="preserve">
+        <v xml:space="preserve">CHQ PAID-SELF-CASH WITHDRAW
+BY SELF - TOLLYGUNGE</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10">
+        <v>11</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2024-07-15</v>
+      </c>
+      <c r="C10" t="str">
+        <v>expense</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Rent</v>
+      </c>
+      <c r="E10" t="str">
+        <v>TXN CHRGS FOR NON MAINTENANCE OF MAB-101</v>
+      </c>
+      <c r="F10">
+        <v>75</v>
+      </c>
+      <c r="G10" t="str">
+        <v>94314202407150077 00000045</v>
+      </c>
+      <c r="H10" t="str" xml:space="preserve">
+        <v xml:space="preserve">TXN CHRGS FOR NON
+MAINTENANCE OF MAB-101</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H10"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -830,7 +965,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/FINANCE.xlsx
+++ b/FINANCE.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -670,9 +670,35 @@
 MAINTENANCE OF MAB-101</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11">
+        <v>12</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2024-07-15</v>
+      </c>
+      <c r="C11" t="str">
+        <v>expense</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Rent</v>
+      </c>
+      <c r="E11" t="str">
+        <v>GST</v>
+      </c>
+      <c r="F11">
+        <v>13.5</v>
+      </c>
+      <c r="G11" t="str">
+        <v>94314202407150077 00000045</v>
+      </c>
+      <c r="H11" t="str">
+        <v>GST to bank</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H11"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -965,7 +991,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/FINANCE.xlsx
+++ b/FINANCE.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -621,7 +621,7 @@
         <v>10</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-05-15</v>
+        <v>2024-07-15</v>
       </c>
       <c r="C9" t="str">
         <v>expense</v>
@@ -696,9 +696,36 @@
         <v>GST to bank</v>
       </c>
     </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12">
+        <v>13</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2024-07-15</v>
+      </c>
+      <c r="C12" t="str">
+        <v>expense</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Salaries &amp; Wages</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Cash Withdrawal</v>
+      </c>
+      <c r="F12">
+        <v>3000</v>
+      </c>
+      <c r="G12" t="str">
+        <v>94314202408200018 00000037</v>
+      </c>
+      <c r="H12" t="str" xml:space="preserve">
+        <v xml:space="preserve">CHQ PAID-SELF-CASH WITHDRAW
+BY SELF - TOLLYGUNGE</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H12"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -991,7 +1018,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/FINANCE.xlsx
+++ b/FINANCE.xlsx
@@ -621,7 +621,7 @@
         <v>10</v>
       </c>
       <c r="B9" t="str">
-        <v>2024-07-15</v>
+        <v>2024-08-20</v>
       </c>
       <c r="C9" t="str">
         <v>expense</v>

--- a/FINANCE.xlsx
+++ b/FINANCE.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -723,9 +723,61 @@
 BY SELF - TOLLYGUNGE</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13">
+        <v>14</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2024-08-23</v>
+      </c>
+      <c r="C13" t="str">
+        <v>expense</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Salaries &amp; Wages</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Cheque Paid – IPSITA KUNDU</v>
+      </c>
+      <c r="F13">
+        <v>500</v>
+      </c>
+      <c r="G13" t="str">
+        <v>STBATCH00007767370</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Cheque Paid – IPSITA KUNDU</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>15</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2025-07-23</v>
+      </c>
+      <c r="C14" t="str">
+        <v>income</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Sales Revenue</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Self Cash Withdrawal</v>
+      </c>
+      <c r="F14">
+        <v>3000</v>
+      </c>
+      <c r="G14" t="str">
+        <v>9431420250723000700000021</v>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H14"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1018,7 +1070,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/FINANCE.xlsx
+++ b/FINANCE.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -757,10 +757,10 @@
         <v>2025-07-23</v>
       </c>
       <c r="C14" t="str">
-        <v>income</v>
+        <v>expense</v>
       </c>
       <c r="D14" t="str">
-        <v>Sales Revenue</v>
+        <v>Salaries &amp; Wages</v>
       </c>
       <c r="E14" t="str">
         <v>Self Cash Withdrawal</v>
@@ -775,9 +775,35 @@
         <v/>
       </c>
     </row>
+    <row r="15">
+      <c r="A15">
+        <v>16</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2025-12-04</v>
+      </c>
+      <c r="C15" t="str">
+        <v>income</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Other Income</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Income Tax Refund NEFT Credit</v>
+      </c>
+      <c r="F15">
+        <v>2310</v>
+      </c>
+      <c r="G15" t="str">
+        <v>2533821129154000</v>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H15"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1070,7 +1096,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/FINANCE.xlsx
+++ b/FINANCE.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -801,9 +801,35 @@
         <v/>
       </c>
     </row>
+    <row r="16">
+      <c r="A16">
+        <v>17</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="C16" t="str">
+        <v>expense</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Self Cash Withdrawal</v>
+      </c>
+      <c r="F16">
+        <v>5000</v>
+      </c>
+      <c r="G16" t="str">
+        <v>9431420260305002100000033</v>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1096,7 +1122,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/FINANCE.xlsx
+++ b/FINANCE.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -827,9 +827,35 @@
         <v/>
       </c>
     </row>
+    <row r="17">
+      <c r="A17">
+        <v>18</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="C17" t="str">
+        <v>expense</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Salaries &amp; Wages</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Cheque Paid – PIYAL GUPTA</v>
+      </c>
+      <c r="F17">
+        <v>5000</v>
+      </c>
+      <c r="G17" t="str">
+        <v>STBATCH00019061618</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H17"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1122,7 +1148,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/FINANCE.xlsx
+++ b/FINANCE.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -853,9 +853,35 @@
         <v/>
       </c>
     </row>
+    <row r="18">
+      <c r="A18">
+        <v>19</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="C18" t="str">
+        <v>expense</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Rent</v>
+      </c>
+      <c r="E18" t="str">
+        <v>MAB CHARGE – March 2026</v>
+      </c>
+      <c r="F18">
+        <v>300</v>
+      </c>
+      <c r="G18" t="str">
+        <v>SCREF00551074829</v>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H18"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1148,7 +1174,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/FINANCE.xlsx
+++ b/FINANCE.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -879,9 +879,35 @@
         <v/>
       </c>
     </row>
+    <row r="19">
+      <c r="A19">
+        <v>20</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="C19" t="str">
+        <v>expense</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Rent</v>
+      </c>
+      <c r="E19" t="str">
+        <v>GST</v>
+      </c>
+      <c r="F19">
+        <v>54</v>
+      </c>
+      <c r="G19" t="str">
+        <v>SCREF00551074829</v>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H19"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1174,7 +1200,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/FINANCE.xlsx
+++ b/FINANCE.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -905,9 +905,61 @@
         <v/>
       </c>
     </row>
+    <row r="20">
+      <c r="A20">
+        <v>21</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="C20" t="str">
+        <v>expense</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Rent</v>
+      </c>
+      <c r="E20" t="str">
+        <v>MAB CHARGE – April 2026</v>
+      </c>
+      <c r="F20">
+        <v>300</v>
+      </c>
+      <c r="G20" t="str">
+        <v>SCREF00573854900</v>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>22</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-05-16</v>
+      </c>
+      <c r="C21" t="str">
+        <v>expense</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Salaries &amp; Wages</v>
+      </c>
+      <c r="E21" t="str">
+        <v>GST</v>
+      </c>
+      <c r="F21">
+        <v>54</v>
+      </c>
+      <c r="G21" t="str">
+        <v>SCREF00573854900</v>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1200,7 +1252,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/FINANCE.xlsx
+++ b/FINANCE.xlsx
@@ -399,31 +399,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:K21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>ID</v>
       </c>
       <c r="B1" t="str">
+        <v>TxnId</v>
+      </c>
+      <c r="C1" t="str">
         <v>Date</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>Type</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>Account</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Description</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Amount</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
+        <v>PaidBy</v>
+      </c>
+      <c r="I1" t="str">
+        <v>PaidTo</v>
+      </c>
+      <c r="J1" t="str">
         <v>Reference</v>
       </c>
-      <c r="H1" t="str">
+      <c r="K1" t="str">
         <v>Notes</v>
       </c>
     </row>
@@ -432,24 +441,33 @@
         <v>3</v>
       </c>
       <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
         <v>2024-06-01</v>
       </c>
-      <c r="C2" t="str">
-        <v>expense</v>
-      </c>
       <c r="D2" t="str">
+        <v>expense</v>
+      </c>
+      <c r="E2" t="str">
         <v>Rent</v>
       </c>
-      <c r="E2" t="str">
+      <c r="F2" t="str">
         <v>MAB CHARGE</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>300</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
         <v>SCREF00124238235</v>
       </c>
-      <c r="H2" t="str">
+      <c r="K2" t="str">
         <v>CA 101 MAB CHARGE</v>
       </c>
     </row>
@@ -458,24 +476,33 @@
         <v>4</v>
       </c>
       <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
         <v>2024-06-01</v>
       </c>
-      <c r="C3" t="str">
-        <v>expense</v>
-      </c>
       <c r="D3" t="str">
+        <v>expense</v>
+      </c>
+      <c r="E3" t="str">
         <v>Rent</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
         <v>GST</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>54</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
         <v>SCREF00124238235</v>
       </c>
-      <c r="H3" t="str">
+      <c r="K3" t="str">
         <v>GST paid to bank</v>
       </c>
     </row>
@@ -484,24 +511,33 @@
         <v>5</v>
       </c>
       <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
         <v>2024-06-15</v>
       </c>
-      <c r="C4" t="str">
+      <c r="D4" t="str">
         <v>income</v>
       </c>
-      <c r="D4" t="str">
+      <c r="E4" t="str">
         <v>Sales Revenue</v>
       </c>
-      <c r="E4" t="str">
+      <c r="F4" t="str">
         <v>Prince Kumar</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>4000</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
         <v>C416789339494</v>
       </c>
-      <c r="H4" t="str" xml:space="preserve">
+      <c r="K4" t="str" xml:space="preserve">
         <v xml:space="preserve">UPI/CR/C416789339494/PRINCE
 KUM/OKHD/PR9525425261
 3@OKHDFCBANK/UPI/HDF54949F9C
@@ -513,24 +549,33 @@
         <v>6</v>
       </c>
       <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
         <v>2024-06-30</v>
       </c>
-      <c r="C5" t="str">
+      <c r="D5" t="str">
         <v>income</v>
       </c>
-      <c r="D5" t="str">
+      <c r="E5" t="str">
         <v>Sales Revenue</v>
       </c>
-      <c r="E5" t="str">
+      <c r="F5" t="str">
         <v>Proposal Development - Jamaica Stock Exchange</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>31500</v>
       </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str" xml:space="preserve">
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str" xml:space="preserve">
         <v xml:space="preserve">NEFT CR-ICIC0SF0002-TUTECK
 TECHNOLOGIES-36783912691DC</v>
       </c>
@@ -540,24 +585,33 @@
         <v>7</v>
       </c>
       <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
         <v>2024-07-01</v>
       </c>
-      <c r="C6" t="str">
-        <v>expense</v>
-      </c>
       <c r="D6" t="str">
+        <v>expense</v>
+      </c>
+      <c r="E6" t="str">
         <v>Rent</v>
       </c>
-      <c r="E6" t="str">
+      <c r="F6" t="str">
         <v>MAB CHARGE</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>300</v>
       </c>
-      <c r="G6" t="str">
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
         <v>SCREF00138682650</v>
       </c>
-      <c r="H6" t="str">
+      <c r="K6" t="str">
         <v>MAB CHARGE - CA 101 MAB CHARGE</v>
       </c>
     </row>
@@ -566,24 +620,33 @@
         <v>8</v>
       </c>
       <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
         <v>2024-07-01</v>
       </c>
-      <c r="C7" t="str">
-        <v>expense</v>
-      </c>
       <c r="D7" t="str">
+        <v>expense</v>
+      </c>
+      <c r="E7" t="str">
         <v>Rent</v>
       </c>
-      <c r="E7" t="str">
+      <c r="F7" t="str">
         <v>GST</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>54</v>
       </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
       <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
         <v>GST paid to bank</v>
       </c>
     </row>
@@ -592,24 +655,33 @@
         <v>9</v>
       </c>
       <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
         <v>2024-07-05</v>
       </c>
-      <c r="C8" t="str">
-        <v>expense</v>
-      </c>
       <c r="D8" t="str">
+        <v>expense</v>
+      </c>
+      <c r="E8" t="str">
         <v>Office Supplies</v>
       </c>
-      <c r="E8" t="str">
+      <c r="F8" t="str">
         <v>Tanveer's Camera Shop</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>16500</v>
       </c>
-      <c r="G8" t="str">
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
         <v>STBATCH000067076 89</v>
       </c>
-      <c r="H8" t="str" xml:space="preserve">
+      <c r="K8" t="str" xml:space="preserve">
         <v xml:space="preserve">CHQ PAID-CTS INWARD  CLEARING
 ZONE 8-TANVIRS THE CAMERA
 SHOPPE-HDFC BANK LTD.-HDFC
@@ -621,24 +693,33 @@
         <v>10</v>
       </c>
       <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
         <v>2024-08-20</v>
       </c>
-      <c r="C9" t="str">
-        <v>expense</v>
-      </c>
       <c r="D9" t="str">
+        <v>expense</v>
+      </c>
+      <c r="E9" t="str">
         <v>Salaries &amp; Wages</v>
       </c>
-      <c r="E9" t="str">
+      <c r="F9" t="str">
         <v>Cash Withdrawal</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>3000</v>
       </c>
-      <c r="G9" t="str">
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
         <v>94314202407150077 00000045</v>
       </c>
-      <c r="H9" t="str" xml:space="preserve">
+      <c r="K9" t="str" xml:space="preserve">
         <v xml:space="preserve">CHQ PAID-SELF-CASH WITHDRAW
 BY SELF - TOLLYGUNGE</v>
       </c>
@@ -648,24 +729,33 @@
         <v>11</v>
       </c>
       <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
         <v>2024-07-15</v>
       </c>
-      <c r="C10" t="str">
-        <v>expense</v>
-      </c>
       <c r="D10" t="str">
+        <v>expense</v>
+      </c>
+      <c r="E10" t="str">
         <v>Rent</v>
       </c>
-      <c r="E10" t="str">
+      <c r="F10" t="str">
         <v>TXN CHRGS FOR NON MAINTENANCE OF MAB-101</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>75</v>
       </c>
-      <c r="G10" t="str">
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
         <v>94314202407150077 00000045</v>
       </c>
-      <c r="H10" t="str" xml:space="preserve">
+      <c r="K10" t="str" xml:space="preserve">
         <v xml:space="preserve">TXN CHRGS FOR NON
 MAINTENANCE OF MAB-101</v>
       </c>
@@ -675,24 +765,33 @@
         <v>12</v>
       </c>
       <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
         <v>2024-07-15</v>
       </c>
-      <c r="C11" t="str">
-        <v>expense</v>
-      </c>
       <c r="D11" t="str">
+        <v>expense</v>
+      </c>
+      <c r="E11" t="str">
         <v>Rent</v>
       </c>
-      <c r="E11" t="str">
+      <c r="F11" t="str">
         <v>GST</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>13.5</v>
       </c>
-      <c r="G11" t="str">
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
         <v>94314202407150077 00000045</v>
       </c>
-      <c r="H11" t="str">
+      <c r="K11" t="str">
         <v>GST to bank</v>
       </c>
     </row>
@@ -701,24 +800,33 @@
         <v>13</v>
       </c>
       <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
         <v>2024-07-15</v>
       </c>
-      <c r="C12" t="str">
-        <v>expense</v>
-      </c>
       <c r="D12" t="str">
+        <v>expense</v>
+      </c>
+      <c r="E12" t="str">
         <v>Salaries &amp; Wages</v>
       </c>
-      <c r="E12" t="str">
+      <c r="F12" t="str">
         <v>Cash Withdrawal</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>3000</v>
       </c>
-      <c r="G12" t="str">
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
         <v>94314202408200018 00000037</v>
       </c>
-      <c r="H12" t="str" xml:space="preserve">
+      <c r="K12" t="str" xml:space="preserve">
         <v xml:space="preserve">CHQ PAID-SELF-CASH WITHDRAW
 BY SELF - TOLLYGUNGE</v>
       </c>
@@ -728,24 +836,33 @@
         <v>14</v>
       </c>
       <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
         <v>2024-08-23</v>
       </c>
-      <c r="C13" t="str">
-        <v>expense</v>
-      </c>
       <c r="D13" t="str">
+        <v>expense</v>
+      </c>
+      <c r="E13" t="str">
         <v>Salaries &amp; Wages</v>
       </c>
-      <c r="E13" t="str">
+      <c r="F13" t="str">
         <v>Cheque Paid – IPSITA KUNDU</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>500</v>
       </c>
-      <c r="G13" t="str">
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
         <v>STBATCH00007767370</v>
       </c>
-      <c r="H13" t="str">
+      <c r="K13" t="str">
         <v>Cheque Paid – IPSITA KUNDU</v>
       </c>
     </row>
@@ -754,24 +871,33 @@
         <v>15</v>
       </c>
       <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
         <v>2025-07-23</v>
       </c>
-      <c r="C14" t="str">
-        <v>expense</v>
-      </c>
       <c r="D14" t="str">
+        <v>expense</v>
+      </c>
+      <c r="E14" t="str">
         <v>Salaries &amp; Wages</v>
       </c>
-      <c r="E14" t="str">
+      <c r="F14" t="str">
         <v>Self Cash Withdrawal</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>3000</v>
       </c>
-      <c r="G14" t="str">
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
         <v>9431420250723000700000021</v>
       </c>
-      <c r="H14" t="str">
+      <c r="K14" t="str">
         <v/>
       </c>
     </row>
@@ -780,24 +906,33 @@
         <v>16</v>
       </c>
       <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
         <v>2025-12-04</v>
       </c>
-      <c r="C15" t="str">
+      <c r="D15" t="str">
         <v>income</v>
       </c>
-      <c r="D15" t="str">
+      <c r="E15" t="str">
         <v>Other Income</v>
       </c>
-      <c r="E15" t="str">
+      <c r="F15" t="str">
         <v>Income Tax Refund NEFT Credit</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>2310</v>
       </c>
-      <c r="G15" t="str">
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
         <v>2533821129154000</v>
       </c>
-      <c r="H15" t="str">
+      <c r="K15" t="str">
         <v/>
       </c>
     </row>
@@ -806,24 +941,33 @@
         <v>17</v>
       </c>
       <c r="B16" t="str">
+        <v/>
+      </c>
+      <c r="C16" t="str">
         <v>2026-03-05</v>
       </c>
-      <c r="C16" t="str">
-        <v>expense</v>
-      </c>
       <c r="D16" t="str">
+        <v>expense</v>
+      </c>
+      <c r="E16" t="str">
         <v>Office Supplies</v>
       </c>
-      <c r="E16" t="str">
+      <c r="F16" t="str">
         <v>Self Cash Withdrawal</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>5000</v>
       </c>
-      <c r="G16" t="str">
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
         <v>9431420260305002100000033</v>
       </c>
-      <c r="H16" t="str">
+      <c r="K16" t="str">
         <v/>
       </c>
     </row>
@@ -832,24 +976,33 @@
         <v>18</v>
       </c>
       <c r="B17" t="str">
+        <v/>
+      </c>
+      <c r="C17" t="str">
         <v>2026-03-06</v>
       </c>
-      <c r="C17" t="str">
-        <v>expense</v>
-      </c>
       <c r="D17" t="str">
+        <v>expense</v>
+      </c>
+      <c r="E17" t="str">
         <v>Salaries &amp; Wages</v>
       </c>
-      <c r="E17" t="str">
+      <c r="F17" t="str">
         <v>Cheque Paid – PIYAL GUPTA</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>5000</v>
       </c>
-      <c r="G17" t="str">
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
         <v>STBATCH00019061618</v>
       </c>
-      <c r="H17" t="str">
+      <c r="K17" t="str">
         <v/>
       </c>
     </row>
@@ -858,24 +1011,33 @@
         <v>19</v>
       </c>
       <c r="B18" t="str">
+        <v/>
+      </c>
+      <c r="C18" t="str">
         <v>2026-04-01</v>
       </c>
-      <c r="C18" t="str">
-        <v>expense</v>
-      </c>
       <c r="D18" t="str">
+        <v>expense</v>
+      </c>
+      <c r="E18" t="str">
         <v>Rent</v>
       </c>
-      <c r="E18" t="str">
+      <c r="F18" t="str">
         <v>MAB CHARGE – March 2026</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>300</v>
       </c>
-      <c r="G18" t="str">
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
         <v>SCREF00551074829</v>
       </c>
-      <c r="H18" t="str">
+      <c r="K18" t="str">
         <v/>
       </c>
     </row>
@@ -884,24 +1046,33 @@
         <v>20</v>
       </c>
       <c r="B19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
         <v>2026-04-01</v>
       </c>
-      <c r="C19" t="str">
-        <v>expense</v>
-      </c>
       <c r="D19" t="str">
+        <v>expense</v>
+      </c>
+      <c r="E19" t="str">
         <v>Rent</v>
       </c>
-      <c r="E19" t="str">
+      <c r="F19" t="str">
         <v>GST</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>54</v>
       </c>
-      <c r="G19" t="str">
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
         <v>SCREF00551074829</v>
       </c>
-      <c r="H19" t="str">
+      <c r="K19" t="str">
         <v/>
       </c>
     </row>
@@ -910,24 +1081,33 @@
         <v>21</v>
       </c>
       <c r="B20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
         <v>2026-05-01</v>
       </c>
-      <c r="C20" t="str">
-        <v>expense</v>
-      </c>
       <c r="D20" t="str">
+        <v>expense</v>
+      </c>
+      <c r="E20" t="str">
         <v>Rent</v>
       </c>
-      <c r="E20" t="str">
+      <c r="F20" t="str">
         <v>MAB CHARGE – April 2026</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>300</v>
       </c>
-      <c r="G20" t="str">
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
         <v>SCREF00573854900</v>
       </c>
-      <c r="H20" t="str">
+      <c r="K20" t="str">
         <v/>
       </c>
     </row>
@@ -936,30 +1116,39 @@
         <v>22</v>
       </c>
       <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
         <v>2026-05-16</v>
       </c>
-      <c r="C21" t="str">
-        <v>expense</v>
-      </c>
       <c r="D21" t="str">
+        <v>expense</v>
+      </c>
+      <c r="E21" t="str">
         <v>Salaries &amp; Wages</v>
       </c>
-      <c r="E21" t="str">
+      <c r="F21" t="str">
         <v>GST</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>54</v>
       </c>
-      <c r="G21" t="str">
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
         <v>SCREF00573854900</v>
       </c>
-      <c r="H21" t="str">
+      <c r="K21" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1243,21 +1432,33 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:C2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>nextId</v>
       </c>
+      <c r="B1" t="str">
+        <v>paidByList</v>
+      </c>
+      <c r="C1" t="str">
+        <v>paidToList</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
         <v>23</v>
       </c>
+      <c r="B2" t="str">
+        <v>[]</v>
+      </c>
+      <c r="C2" t="str">
+        <v>[]</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
   </ignoredErrors>
 </worksheet>
 </file>